--- a/Reports/sanityReport.xlsx
+++ b/Reports/sanityReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Test Case</t>
   </si>
@@ -26,31 +26,43 @@
     <t>login</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>13735 ms</t>
-  </si>
-  <si>
-    <t>createLead</t>
-  </si>
-  <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>49747 ms</t>
+    <t>9769 ms</t>
   </si>
   <si>
-    <t>createView</t>
+    <t>createLead_WithOnlyRequiredFields</t>
   </si>
   <si>
-    <t>26701 ms</t>
+    <t>26893 ms</t>
   </si>
   <si>
     <t>note</t>
   </si>
   <si>
-    <t>1114 ms</t>
+    <t>30750 ms</t>
+  </si>
+  <si>
+    <t>addTask</t>
+  </si>
+  <si>
+    <t>33405 ms</t>
+  </si>
+  <si>
+    <t>addMeeting</t>
+  </si>
+  <si>
+    <t>15769 ms</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>1148 ms</t>
   </si>
 </sst>
 </file>
@@ -95,7 +107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -125,32 +137,54 @@
         <v>6</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>4</v>
       </c>
       <c r="C5" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
         <v>12</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
